--- a/artfynd/A 31303-2023 artfynd.xlsx
+++ b/artfynd/A 31303-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130695480</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>130695482</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31303-2023 artfynd.xlsx
+++ b/artfynd/A 31303-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130695480</v>
       </c>
       <c r="B2" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>130695482</v>
       </c>
       <c r="B3" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31303-2023 artfynd.xlsx
+++ b/artfynd/A 31303-2023 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>130695482</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
